--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_swmm.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_swmm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAEFC9C-8C00-4929-AB95-1C97A3DCCB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111BC0A2-D04B-4FD8-96FA-4EE3C48A48A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="18">
   <si>
     <t>CPU</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>standard</t>
-  </si>
-  <si>
-    <t>hpc_time_min_per_sim</t>
   </si>
 </sst>
 </file>
@@ -314,7 +311,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -337,9 +334,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Input" xfId="1" builtinId="20"/>
@@ -347,7 +341,7 @@
     <cellStyle name="Note" xfId="3" builtinId="10"/>
     <cellStyle name="Output" xfId="2" builtinId="21"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="16">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -414,25 +408,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -676,23 +651,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A4495C6-64F1-4654-82C3-1417CFDBC1D1}" name="Table1" displayName="Table1" ref="A1:M8" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A1:M8" xr:uid="{1A4495C6-64F1-4654-82C3-1417CFDBC1D1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A4495C6-64F1-4654-82C3-1417CFDBC1D1}" name="Table1" displayName="Table1" ref="A1:L8" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:L8" xr:uid="{1A4495C6-64F1-4654-82C3-1417CFDBC1D1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L8">
     <sortCondition ref="E1:E8"/>
   </sortState>
-  <tableColumns count="13">
-    <tableColumn id="11" xr3:uid="{3DECB62C-AAF2-4EC7-8598-5E8776D4B845}" name="hardware_utilization_strategy" dataDxfId="12" dataCellStyle="Note"/>
-    <tableColumn id="9" xr3:uid="{047B8296-C28F-43DA-A753-CC6445B34CE4}" name="device" dataDxfId="11" dataCellStyle="Note"/>
-    <tableColumn id="1" xr3:uid="{16000747-EB63-4EDF-971B-D9460636B6A5}" name="run_mode" dataDxfId="10" dataCellStyle="Input"/>
-    <tableColumn id="2" xr3:uid="{09DC1F4B-B2B0-493A-B83E-1D7D4EA31F4C}" name="n_nodes" dataDxfId="9" dataCellStyle="Input"/>
-    <tableColumn id="3" xr3:uid="{3A65E5E5-CB8B-4698-A27C-21DF3A95D49A}" name="n_mpi_procs" dataDxfId="8" dataCellStyle="Input"/>
-    <tableColumn id="4" xr3:uid="{D366E835-7967-45B3-94DD-92B04C3126AA}" name="n_omp_threads" dataDxfId="7" dataCellStyle="Input"/>
-    <tableColumn id="8" xr3:uid="{53D9FE6F-92F7-4A3A-B94F-6A698F029BE0}" name="n_gpus" dataDxfId="6" dataCellStyle="Input"/>
-    <tableColumn id="12" xr3:uid="{97D9BCE9-C2EB-487D-9081-3F6B6CACB117}" name="hpc_ensemble_partition" dataDxfId="5" dataCellStyle="Input"/>
-    <tableColumn id="13" xr3:uid="{96650528-E8C5-445B-8564-B12E25175139}" name="hpc_time_min_per_sim" dataDxfId="4" dataCellStyle="Input">
-      <calculatedColumnFormula>60*6</calculatedColumnFormula>
-    </tableColumn>
+  <tableColumns count="12">
+    <tableColumn id="11" xr3:uid="{3DECB62C-AAF2-4EC7-8598-5E8776D4B845}" name="hardware_utilization_strategy" dataDxfId="11" dataCellStyle="Note"/>
+    <tableColumn id="9" xr3:uid="{047B8296-C28F-43DA-A753-CC6445B34CE4}" name="device" dataDxfId="10" dataCellStyle="Note"/>
+    <tableColumn id="1" xr3:uid="{16000747-EB63-4EDF-971B-D9460636B6A5}" name="run_mode" dataDxfId="9" dataCellStyle="Input"/>
+    <tableColumn id="2" xr3:uid="{09DC1F4B-B2B0-493A-B83E-1D7D4EA31F4C}" name="n_nodes" dataDxfId="8" dataCellStyle="Input"/>
+    <tableColumn id="3" xr3:uid="{3A65E5E5-CB8B-4698-A27C-21DF3A95D49A}" name="n_mpi_procs" dataDxfId="7" dataCellStyle="Input"/>
+    <tableColumn id="4" xr3:uid="{D366E835-7967-45B3-94DD-92B04C3126AA}" name="n_omp_threads" dataDxfId="6" dataCellStyle="Input"/>
+    <tableColumn id="8" xr3:uid="{53D9FE6F-92F7-4A3A-B94F-6A698F029BE0}" name="n_gpus" dataDxfId="5" dataCellStyle="Input"/>
+    <tableColumn id="12" xr3:uid="{97D9BCE9-C2EB-487D-9081-3F6B6CACB117}" name="hpc_ensemble_partition" dataDxfId="4" dataCellStyle="Input"/>
     <tableColumn id="6" xr3:uid="{F6B7A6B4-BD4B-4406-BCB7-C3DBCC48FA6B}" name="total_OpenMP_threads" dataDxfId="3" dataCellStyle="Output">
       <calculatedColumnFormula>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</calculatedColumnFormula>
     </tableColumn>
@@ -973,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
@@ -982,13 +954,13 @@
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="28.28515625" customWidth="1"/>
-    <col min="10" max="10" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="28.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1013,23 +985,20 @@
       <c r="H1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="12" t="s">
-        <v>18</v>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -1054,28 +1023,24 @@
       <c r="H2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="4">
-        <f>60*6</f>
-        <v>360</v>
+      <c r="I2" s="5">
+        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
+        <v>1</v>
       </c>
       <c r="J2" s="5">
-        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
-        <v>1</v>
-      </c>
-      <c r="K2" s="5">
         <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
         <v>1</v>
       </c>
-      <c r="L2" s="6">
+      <c r="K2" s="6">
         <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
         <v>1</v>
       </c>
-      <c r="M2" t="b">
+      <c r="L2" t="b">
         <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -1100,28 +1065,24 @@
       <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="4">
-        <f>60*6</f>
-        <v>360</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="I3" s="5">
         <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
         <v>2</v>
       </c>
-      <c r="K3" s="5">
+      <c r="J3" s="5">
         <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
         <v>2</v>
       </c>
-      <c r="L3" s="6">
+      <c r="K3" s="6">
         <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
         <v>2</v>
       </c>
-      <c r="M3" t="b">
+      <c r="L3" t="b">
         <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -1146,28 +1107,24 @@
       <c r="H4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="4">
-        <f>60*6</f>
-        <v>360</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="I4" s="5">
         <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
         <v>4</v>
       </c>
-      <c r="K4" s="5">
+      <c r="J4" s="5">
         <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
         <v>4</v>
       </c>
-      <c r="L4" s="6">
+      <c r="K4" s="6">
         <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
         <v>4</v>
       </c>
-      <c r="M4" t="b">
+      <c r="L4" t="b">
         <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>2</v>
       </c>
@@ -1192,28 +1149,24 @@
       <c r="H5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="4">
-        <f>60*6</f>
-        <v>360</v>
-      </c>
-      <c r="J5" s="5">
+      <c r="I5" s="5">
         <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
         <v>8</v>
       </c>
-      <c r="K5" s="5">
+      <c r="J5" s="5">
         <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
         <v>8</v>
       </c>
-      <c r="L5" s="6">
+      <c r="K5" s="6">
         <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
         <v>8</v>
       </c>
-      <c r="M5" t="b">
+      <c r="L5" t="b">
         <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>2</v>
       </c>
@@ -1238,28 +1191,24 @@
       <c r="H6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="4">
-        <f>60*6</f>
-        <v>360</v>
-      </c>
-      <c r="J6" s="5">
+      <c r="I6" s="5">
         <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
         <v>16</v>
       </c>
-      <c r="K6" s="5">
+      <c r="J6" s="5">
         <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
         <v>16</v>
       </c>
-      <c r="L6" s="6">
+      <c r="K6" s="6">
         <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
         <v>16</v>
       </c>
-      <c r="M6" t="b">
+      <c r="L6" t="b">
         <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>2</v>
       </c>
@@ -1284,28 +1233,24 @@
       <c r="H7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="4">
-        <f>60*6</f>
-        <v>360</v>
-      </c>
-      <c r="J7" s="5">
+      <c r="I7" s="5">
         <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
         <v>32</v>
       </c>
-      <c r="K7" s="5">
+      <c r="J7" s="5">
         <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
         <v>32</v>
       </c>
-      <c r="L7" s="6">
+      <c r="K7" s="6">
         <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
         <v>32</v>
       </c>
-      <c r="M7" t="b">
+      <c r="L7" t="b">
         <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>2</v>
       </c>
@@ -1330,23 +1275,19 @@
       <c r="H8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="4">
-        <f>60*6</f>
-        <v>360</v>
-      </c>
-      <c r="J8" s="5">
+      <c r="I8" s="5">
         <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
         <v>64</v>
       </c>
-      <c r="K8" s="5">
+      <c r="J8" s="5">
         <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
         <v>64</v>
       </c>
-      <c r="L8" s="6">
+      <c r="K8" s="6">
         <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
         <v>64</v>
       </c>
-      <c r="M8" t="b">
+      <c r="L8" t="b">
         <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
         <v>1</v>
       </c>

--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_swmm.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_swmm.xlsx
@@ -1,147 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\dcl3nd\dev\TRITON-SWMM_toolkit\test_data\norfolk_coastal_flooding\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111BC0A2-D04B-4FD8-96FA-4EE3C48A48A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="18">
-  <si>
-    <t>CPU</t>
-  </si>
-  <si>
-    <t>Baseline - 1 CPU</t>
-  </si>
-  <si>
-    <t>Multi-CPU - OMP</t>
-  </si>
-  <si>
-    <t>devices_per_node</t>
-  </si>
-  <si>
-    <t>hardware_utilization_strategy</t>
-  </si>
-  <si>
-    <t>device</t>
-  </si>
-  <si>
-    <t>total_OpenMP_threads</t>
-  </si>
-  <si>
-    <t>total_devices</t>
-  </si>
-  <si>
-    <t>run_mode</t>
-  </si>
-  <si>
-    <t>n_nodes</t>
-  </si>
-  <si>
-    <t>n_mpi_procs</t>
-  </si>
-  <si>
-    <t>n_omp_threads</t>
-  </si>
-  <si>
-    <t>n_gpus</t>
-  </si>
-  <si>
-    <t>serial</t>
-  </si>
-  <si>
-    <t>openmp</t>
-  </si>
-  <si>
-    <t>check</t>
-  </si>
-  <si>
-    <t>hpc_ensemble_partition</t>
-  </si>
-  <si>
-    <t>standard</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -306,40 +226,40 @@
     </border>
   </borders>
   <cellStyleXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Input" xfId="1" builtinId="20"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Output" xfId="2" builtinId="21"/>
     <cellStyle name="Note" xfId="3" builtinId="10"/>
-    <cellStyle name="Output" xfId="2" builtinId="21"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
@@ -347,7 +267,7 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -367,7 +287,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -389,7 +309,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -411,7 +331,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -428,7 +348,7 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -446,7 +366,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -468,7 +388,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -490,7 +410,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -513,24 +433,21 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color theme="1"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -548,7 +465,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -570,7 +487,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -597,7 +514,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -620,7 +537,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -639,42 +556,102 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A4495C6-64F1-4654-82C3-1417CFDBC1D1}" name="Table1" displayName="Table1" ref="A1:L8" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:L8" xr:uid="{1A4495C6-64F1-4654-82C3-1417CFDBC1D1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:L8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:L8"/>
+  <sortState ref="A2:L8">
     <sortCondition ref="E1:E8"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="11" xr3:uid="{3DECB62C-AAF2-4EC7-8598-5E8776D4B845}" name="hardware_utilization_strategy" dataDxfId="11" dataCellStyle="Note"/>
-    <tableColumn id="9" xr3:uid="{047B8296-C28F-43DA-A753-CC6445B34CE4}" name="device" dataDxfId="10" dataCellStyle="Note"/>
-    <tableColumn id="1" xr3:uid="{16000747-EB63-4EDF-971B-D9460636B6A5}" name="run_mode" dataDxfId="9" dataCellStyle="Input"/>
-    <tableColumn id="2" xr3:uid="{09DC1F4B-B2B0-493A-B83E-1D7D4EA31F4C}" name="n_nodes" dataDxfId="8" dataCellStyle="Input"/>
-    <tableColumn id="3" xr3:uid="{3A65E5E5-CB8B-4698-A27C-21DF3A95D49A}" name="n_mpi_procs" dataDxfId="7" dataCellStyle="Input"/>
-    <tableColumn id="4" xr3:uid="{D366E835-7967-45B3-94DD-92B04C3126AA}" name="n_omp_threads" dataDxfId="6" dataCellStyle="Input"/>
-    <tableColumn id="8" xr3:uid="{53D9FE6F-92F7-4A3A-B94F-6A698F029BE0}" name="n_gpus" dataDxfId="5" dataCellStyle="Input"/>
-    <tableColumn id="12" xr3:uid="{97D9BCE9-C2EB-487D-9081-3F6B6CACB117}" name="hpc_ensemble_partition" dataDxfId="4" dataCellStyle="Input"/>
-    <tableColumn id="6" xr3:uid="{F6B7A6B4-BD4B-4406-BCB7-C3DBCC48FA6B}" name="total_OpenMP_threads" dataDxfId="3" dataCellStyle="Output">
+    <tableColumn id="11" name="hardware_utilization_strategy" dataDxfId="11" dataCellStyle="Note"/>
+    <tableColumn id="9" name="device" dataDxfId="10" dataCellStyle="Note"/>
+    <tableColumn id="1" name="run_mode" dataDxfId="9" dataCellStyle="Input"/>
+    <tableColumn id="2" name="n_nodes" dataDxfId="8" dataCellStyle="Input"/>
+    <tableColumn id="3" name="n_mpi_procs" dataDxfId="7" dataCellStyle="Input"/>
+    <tableColumn id="4" name="n_omp_threads" dataDxfId="6" dataCellStyle="Input"/>
+    <tableColumn id="8" name="n_gpus" dataDxfId="5" dataCellStyle="Input"/>
+    <tableColumn id="12" name="hpc_ensemble_partition" dataDxfId="4" dataCellStyle="Input"/>
+    <tableColumn id="6" name="total_OpenMP_threads" dataDxfId="3" dataCellStyle="Output">
       <calculatedColumnFormula>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8B064801-C992-4C19-AF9B-73CC7D0951B1}" name="total_devices" dataDxfId="2" dataCellStyle="Output">
+    <tableColumn id="7" name="total_devices" dataDxfId="2" dataCellStyle="Output">
       <calculatedColumnFormula>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C813D3D6-6AEA-4168-A5C0-6FD56BB1D36D}" name="devices_per_node" dataDxfId="1" dataCellStyle="Output">
+    <tableColumn id="10" name="devices_per_node" dataDxfId="1" dataCellStyle="Output">
       <calculatedColumnFormula>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{47E652A1-51DD-4A45-9FB0-F72E592EF0D3}" name="check" dataDxfId="0">
+    <tableColumn id="5" name="check" dataDxfId="0">
       <calculatedColumnFormula>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -944,358 +921,468 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="28.28515625" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col width="29.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9.28515625" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="22.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="28.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="28.28515625" customWidth="1" min="7" max="8"/>
+    <col width="24.7109375" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="19.85546875" bestFit="1" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sa_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>hardware_utilization_strategy</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>run_mode</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>n_nodes</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>n_mpi_procs</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>n_omp_threads</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>n_gpus</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>hpc_ensemble_partition</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>total_OpenMP_threads</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>total_devices</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>devices_per_node</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Baseline - 1 CPU</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="J2" s="5">
+        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="K2" s="5">
+        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="L2" s="6">
+        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="M2">
+        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Multi-CPU - OMP</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>openmp</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="J3" s="5">
+        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="K3" s="5">
+        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="L3" s="6">
+        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="M3">
+        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Multi-CPU - OMP</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>openmp</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="J4" s="5">
+        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="K4" s="5">
+        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="L4" s="6">
+        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="M4">
+        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Multi-CPU - OMP</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>openmp</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="J5" s="5">
+        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="K5" s="5">
+        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="L5" s="6">
+        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="M5">
+        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Multi-CPU - OMP</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>openmp</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="J6" s="5">
+        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="K6" s="5">
+        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="L6" s="6">
+        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="M6">
+        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Multi-CPU - OMP</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>openmp</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="J7" s="5">
+        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
+        <v/>
+      </c>
+      <c r="K7" s="5">
+        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
+        <v/>
+      </c>
+      <c r="L7" s="6">
+        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+      <c r="M7">
+        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Multi-CPU - OMP</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>openmp</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="9">
-        <v>1</v>
-      </c>
-      <c r="E2" s="9">
-        <v>1</v>
-      </c>
-      <c r="F2" s="9">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="J8" s="5">
         <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
-        <v>1</v>
-      </c>
-      <c r="J2" s="5">
+        <v/>
+      </c>
+      <c r="K8" s="5">
         <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
-        <v>1</v>
-      </c>
-      <c r="K2" s="6">
+        <v/>
+      </c>
+      <c r="L8" s="6">
         <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
-        <v>1</v>
-      </c>
-      <c r="L2" t="b">
+        <v/>
+      </c>
+      <c r="M8">
         <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="9">
-        <v>1</v>
-      </c>
-      <c r="E3" s="9">
-        <v>1</v>
-      </c>
-      <c r="F3" s="9">
-        <v>2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="5">
-        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
-        <v>2</v>
-      </c>
-      <c r="K3" s="6">
-        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
-        <v>2</v>
-      </c>
-      <c r="L3" t="b">
-        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="9">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9">
-        <v>1</v>
-      </c>
-      <c r="F4" s="9">
-        <v>4</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="5">
-        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
-        <v>4</v>
-      </c>
-      <c r="K4" s="6">
-        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
-        <v>4</v>
-      </c>
-      <c r="L4" t="b">
-        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="9">
-        <v>1</v>
-      </c>
-      <c r="E5" s="9">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9">
-        <v>8</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="5">
-        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
-        <v>8</v>
-      </c>
-      <c r="J5" s="5">
-        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
-        <v>8</v>
-      </c>
-      <c r="K5" s="6">
-        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
-        <v>8</v>
-      </c>
-      <c r="L5" t="b">
-        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="9">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9">
-        <v>1</v>
-      </c>
-      <c r="F6" s="9">
-        <v>16</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="5">
-        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
-        <v>16</v>
-      </c>
-      <c r="J6" s="5">
-        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
-        <v>16</v>
-      </c>
-      <c r="K6" s="6">
-        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
-        <v>16</v>
-      </c>
-      <c r="L6" t="b">
-        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="9">
-        <v>1</v>
-      </c>
-      <c r="E7" s="9">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9">
-        <v>32</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="5">
-        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
-        <v>32</v>
-      </c>
-      <c r="J7" s="5">
-        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
-        <v>32</v>
-      </c>
-      <c r="K7" s="6">
-        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
-        <v>32</v>
-      </c>
-      <c r="L7" t="b">
-        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="9">
-        <v>1</v>
-      </c>
-      <c r="E8" s="9">
-        <v>1</v>
-      </c>
-      <c r="F8" s="9">
-        <v>64</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="5">
-        <f>Table1[[#This Row],[n_mpi_procs]]*Table1[[#This Row],[n_omp_threads]]</f>
-        <v>64</v>
-      </c>
-      <c r="J8" s="5">
-        <f>Table1[[#This Row],[n_omp_threads]]*Table1[[#This Row],[n_mpi_procs]]</f>
-        <v>64</v>
-      </c>
-      <c r="K8" s="6">
-        <f>Table1[[#This Row],[total_devices]]/Table1[[#This Row],[n_nodes]]</f>
-        <v>64</v>
-      </c>
-      <c r="L8" t="b">
-        <f>Table1[[#This Row],[n_mpi_procs]]&gt;=Table1[[#This Row],[n_nodes]]</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_swmm.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_swmm.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>hpc_ensemble_partition</t>
+          <t>analysis.hpc_ensemble_partition</t>
         </is>
       </c>
     </row>
